--- a/samples/reports/delivery-note/template.xlsx
+++ b/samples/reports/delivery-note/template.xlsx
@@ -6,7 +6,7 @@
     <x:definedName name="_xlnm.Print_Titles" localSheetId="0">'納品書'!$1:$7</x:definedName>
   </x:definedNames>
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="納品書" sheetId="1" r:id="R6be8477a6f5d4d2a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="納品書" sheetId="1" r:id="Rca61988e7ca34452"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -1764,5 +1764,9 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:pageSetup paperSize="9" scale="100" pageOrder="downThenOver" orientation="portrait"/>
+  <x:headerFooter>
+    <x:oddHeader>&amp;R&amp;A</x:oddHeader>
+    <x:oddFooter>&amp;L&amp;D&amp;C&amp;P / &amp;N ページ&amp;R&amp;"MS PGothic,Bold"サンプル</x:oddFooter>
+  </x:headerFooter>
 </x:worksheet>
 </file>